--- a/synoptic/data/DOC_TDN.xlsx
+++ b/synoptic/data/DOC_TDN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\PR-wetlands\synoptic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AB0D707-6842-41A7-A191-C2E646AEEBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6A2975-67A5-4198-8EFB-86225C45D58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{54C87060-B7A1-4CAD-9E1A-36329F3319CD}"/>
   </bookViews>
@@ -449,13 +449,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A77AF44-731D-4D46-9781-1A1FF25B2201}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -469,7 +469,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -483,7 +483,7 @@
         <v>2.7050000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>2.778</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -511,7 +511,7 @@
         <v>2.863</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -525,7 +525,7 @@
         <v>2.589</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -539,7 +539,7 @@
         <v>2.714</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -553,7 +553,7 @@
         <v>2.7679999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -567,7 +567,7 @@
         <v>3.0049999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -581,7 +581,7 @@
         <v>3.0539999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -595,7 +595,7 @@
         <v>3.113</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -608,8 +608,12 @@
       <c r="D11">
         <v>1.5209999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <f>AVERAGE(C11:C22)</f>
+        <v>20.999583333333337</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -623,7 +627,7 @@
         <v>1.5940000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -637,7 +641,7 @@
         <v>1.5980000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -651,7 +655,7 @@
         <v>1.216</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -665,7 +669,7 @@
         <v>1.234</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -679,7 +683,7 @@
         <v>1.2230000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -693,7 +697,7 @@
         <v>1.3320000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -707,7 +711,7 @@
         <v>1.365</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -721,7 +725,7 @@
         <v>1.363</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -735,7 +739,7 @@
         <v>1.2150000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -749,7 +753,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -763,7 +767,7 @@
         <v>1.343</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1</v>
       </c>
@@ -776,8 +780,12 @@
       <c r="D23">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23">
+        <f>AVERAGE(C23:C34)</f>
+        <v>29.574166666666667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1</v>
       </c>
@@ -791,7 +799,7 @@
         <v>1.5609999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -805,7 +813,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1</v>
       </c>
@@ -819,7 +827,7 @@
         <v>1.3979999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1</v>
       </c>
@@ -833,7 +841,7 @@
         <v>1.3440000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1</v>
       </c>
@@ -847,7 +855,7 @@
         <v>1.3979999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -861,7 +869,7 @@
         <v>1.571</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1</v>
       </c>
@@ -875,7 +883,7 @@
         <v>1.6160000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1</v>
       </c>
@@ -889,7 +897,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1</v>
       </c>
